--- a/Тематика для рассылки/Пробная версия/02_Сводный_реестр_ПРИМЕР.xlsx
+++ b/Тематика для рассылки/Пробная версия/02_Сводный_реестр_ПРИМЕР.xlsx
@@ -42,12 +42,12 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="00221F1F"/>
       <sz val="20"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <color rgb="0017324D"/>
+      <color rgb="00221F1F"/>
       <sz val="11"/>
     </font>
     <font>
@@ -57,7 +57,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -66,27 +66,32 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0017324D"/>
+        <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF0DA"/>
+        <fgColor rgb="0026BBA8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EAF3F6"/>
+        <fgColor rgb="0040B870"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F7FA"/>
+        <fgColor rgb="00F2F5F3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
+        <fgColor rgb="00F0F8F4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00221F1F"/>
       </patternFill>
     </fill>
   </fills>
@@ -102,38 +107,92 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <dxfs count="4">
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <color rgb="00221F1F"/>
+        <sz val="11"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <b val="1"/>
+        <color rgb="00FFFFFF"/>
+        <sz val="11"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00221F1F"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="medium">
+          <color rgb="0026BBA8"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00F0F8F4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
+  <tableStyles count="1" defaultTableStyle="RozumTable" defaultPivotStyle="PivotStyleLight16">
+    <tableStyle name="RozumTable" pivot="0" table="1">
+      <tableStyleElement type="wholeTable" dxfId="0"/>
+      <tableStyleElement type="headerRow" dxfId="1"/>
+      <tableStyleElement type="firstRowStripe" size="1" dxfId="2"/>
+      <tableStyleElement type="secondRowStripe" size="1" dxfId="3"/>
+    </tableStyle>
+  </tableStyles>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -205,6 +264,156 @@
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>57150</colOff>
+      <row>0</row>
+      <rowOff>142875</rowOff>
+    </from>
+    <ext cx="1619250" cy="333375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>57150</colOff>
+      <row>0</row>
+      <rowOff>142875</rowOff>
+    </from>
+    <ext cx="1619250" cy="333375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>57150</colOff>
+      <row>0</row>
+      <rowOff>142875</rowOff>
+    </from>
+    <ext cx="1619250" cy="333375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>57150</colOff>
+      <row>0</row>
+      <rowOff>142875</rowOff>
+    </from>
+    <ext cx="1619250" cy="333375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>57150</colOff>
+      <row>0</row>
+      <rowOff>142875</rowOff>
+    </from>
+    <ext cx="1619250" cy="333375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="LecturerTopicRegistry" displayName="LecturerTopicRegistry" ref="A5:I14" headerRowCount="1">
   <autoFilter ref="A5:I14"/>
@@ -219,7 +428,7 @@
     <tableColumn id="8" name="Дата анкеты"/>
     <tableColumn id="9" name="Файл ответа"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+  <tableStyleInfo name="RozumTable" showRowStripes="0"/>
 </table>
 </file>
 
@@ -235,7 +444,7 @@
     <tableColumn id="6" name="Частично"/>
     <tableColumn id="7" name="Покрытие темы"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+  <tableStyleInfo name="RozumTable" showRowStripes="0"/>
 </table>
 </file>
 
@@ -250,7 +459,7 @@
     <tableColumn id="5" name="Тем частично"/>
     <tableColumn id="6" name="Файл ответа"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+  <tableStyleInfo name="RozumTable" showRowStripes="0"/>
 </table>
 </file>
 
@@ -263,291 +472,291 @@
     <tableColumn id="3" name="Полное название программы"/>
     <tableColumn id="4" name="Файл-источник"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+  <tableStyleInfo name="RozumTable" showRowStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
-  <a:themeElements>
-    <a:clrScheme name="Office">
-      <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="1F497D"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="EEECE1"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="4F81BD"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="C0504D"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="9BBB59"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="8064A2"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="4BACC6"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="F79646"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="0000FF"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="800080"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Cambria"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme name="Office">
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="35000">
-              <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
-        </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="40000">
-              <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
-        </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-</a:theme>
+<ns0:theme xmlns:ns0="http://schemas.openxmlformats.org/drawingml/2006/main" name="Rozum">
+  <ns0:themeElements>
+    <ns0:clrScheme name="Rozum">
+      <ns0:dk1>
+        <ns0:srgbClr val="221F1F"/>
+      </ns0:dk1>
+      <ns0:lt1>
+        <ns0:srgbClr val="FFFFFF"/>
+      </ns0:lt1>
+      <ns0:dk2>
+        <ns0:srgbClr val="221F1F"/>
+      </ns0:dk2>
+      <ns0:lt2>
+        <ns0:srgbClr val="F0F8F4"/>
+      </ns0:lt2>
+      <ns0:accent1>
+        <ns0:srgbClr val="26BBA8"/>
+      </ns0:accent1>
+      <ns0:accent2>
+        <ns0:srgbClr val="40B870"/>
+      </ns0:accent2>
+      <ns0:accent3>
+        <ns0:srgbClr val="008685"/>
+      </ns0:accent3>
+      <ns0:accent4>
+        <ns0:srgbClr val="009763"/>
+      </ns0:accent4>
+      <ns0:accent5>
+        <ns0:srgbClr val="60756C"/>
+      </ns0:accent5>
+      <ns0:accent6>
+        <ns0:srgbClr val="DDF2E5"/>
+      </ns0:accent6>
+      <ns0:hlink>
+        <ns0:srgbClr val="008685"/>
+      </ns0:hlink>
+      <ns0:folHlink>
+        <ns0:srgbClr val="009763"/>
+      </ns0:folHlink>
+    </ns0:clrScheme>
+    <ns0:fontScheme name="Office">
+      <ns0:majorFont>
+        <ns0:latin typeface="Cambria"/>
+        <ns0:ea typeface=""/>
+        <ns0:cs typeface=""/>
+        <ns0:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <ns0:font script="Hang" typeface="맑은 고딕"/>
+        <ns0:font script="Hans" typeface="宋体"/>
+        <ns0:font script="Hant" typeface="新細明體"/>
+        <ns0:font script="Arab" typeface="Times New Roman"/>
+        <ns0:font script="Hebr" typeface="Times New Roman"/>
+        <ns0:font script="Thai" typeface="Tahoma"/>
+        <ns0:font script="Ethi" typeface="Nyala"/>
+        <ns0:font script="Beng" typeface="Vrinda"/>
+        <ns0:font script="Gujr" typeface="Shruti"/>
+        <ns0:font script="Khmr" typeface="MoolBoran"/>
+        <ns0:font script="Knda" typeface="Tunga"/>
+        <ns0:font script="Guru" typeface="Raavi"/>
+        <ns0:font script="Cans" typeface="Euphemia"/>
+        <ns0:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <ns0:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <ns0:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <ns0:font script="Thaa" typeface="MV Boli"/>
+        <ns0:font script="Deva" typeface="Mangal"/>
+        <ns0:font script="Telu" typeface="Gautami"/>
+        <ns0:font script="Taml" typeface="Latha"/>
+        <ns0:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <ns0:font script="Orya" typeface="Kalinga"/>
+        <ns0:font script="Mlym" typeface="Kartika"/>
+        <ns0:font script="Laoo" typeface="DokChampa"/>
+        <ns0:font script="Sinh" typeface="Iskoola Pota"/>
+        <ns0:font script="Mong" typeface="Mongolian Baiti"/>
+        <ns0:font script="Viet" typeface="Times New Roman"/>
+        <ns0:font script="Uigh" typeface="Microsoft Uighur"/>
+      </ns0:majorFont>
+      <ns0:minorFont>
+        <ns0:latin typeface="Calibri"/>
+        <ns0:ea typeface=""/>
+        <ns0:cs typeface=""/>
+        <ns0:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <ns0:font script="Hang" typeface="맑은 고딕"/>
+        <ns0:font script="Hans" typeface="宋体"/>
+        <ns0:font script="Hant" typeface="新細明體"/>
+        <ns0:font script="Arab" typeface="Arial"/>
+        <ns0:font script="Hebr" typeface="Arial"/>
+        <ns0:font script="Thai" typeface="Tahoma"/>
+        <ns0:font script="Ethi" typeface="Nyala"/>
+        <ns0:font script="Beng" typeface="Vrinda"/>
+        <ns0:font script="Gujr" typeface="Shruti"/>
+        <ns0:font script="Khmr" typeface="DaunPenh"/>
+        <ns0:font script="Knda" typeface="Tunga"/>
+        <ns0:font script="Guru" typeface="Raavi"/>
+        <ns0:font script="Cans" typeface="Euphemia"/>
+        <ns0:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <ns0:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <ns0:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <ns0:font script="Thaa" typeface="MV Boli"/>
+        <ns0:font script="Deva" typeface="Mangal"/>
+        <ns0:font script="Telu" typeface="Gautami"/>
+        <ns0:font script="Taml" typeface="Latha"/>
+        <ns0:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <ns0:font script="Orya" typeface="Kalinga"/>
+        <ns0:font script="Mlym" typeface="Kartika"/>
+        <ns0:font script="Laoo" typeface="DokChampa"/>
+        <ns0:font script="Sinh" typeface="Iskoola Pota"/>
+        <ns0:font script="Mong" typeface="Mongolian Baiti"/>
+        <ns0:font script="Viet" typeface="Arial"/>
+        <ns0:font script="Uigh" typeface="Microsoft Uighur"/>
+      </ns0:minorFont>
+    </ns0:fontScheme>
+    <ns0:fmtScheme name="Office">
+      <ns0:fillStyleLst>
+        <ns0:solidFill>
+          <ns0:schemeClr val="phClr"/>
+        </ns0:solidFill>
+        <ns0:gradFill rotWithShape="1">
+          <ns0:gsLst>
+            <ns0:gs pos="0">
+              <ns0:schemeClr val="phClr">
+                <ns0:tint val="50000"/>
+                <ns0:satMod val="300000"/>
+              </ns0:schemeClr>
+            </ns0:gs>
+            <ns0:gs pos="35000">
+              <ns0:schemeClr val="phClr">
+                <ns0:tint val="37000"/>
+                <ns0:satMod val="300000"/>
+              </ns0:schemeClr>
+            </ns0:gs>
+            <ns0:gs pos="100000">
+              <ns0:schemeClr val="phClr">
+                <ns0:tint val="15000"/>
+                <ns0:satMod val="350000"/>
+              </ns0:schemeClr>
+            </ns0:gs>
+          </ns0:gsLst>
+          <ns0:lin ang="16200000" scaled="1"/>
+        </ns0:gradFill>
+        <ns0:gradFill rotWithShape="1">
+          <ns0:gsLst>
+            <ns0:gs pos="0">
+              <ns0:schemeClr val="phClr">
+                <ns0:shade val="51000"/>
+                <ns0:satMod val="130000"/>
+              </ns0:schemeClr>
+            </ns0:gs>
+            <ns0:gs pos="80000">
+              <ns0:schemeClr val="phClr">
+                <ns0:shade val="93000"/>
+                <ns0:satMod val="130000"/>
+              </ns0:schemeClr>
+            </ns0:gs>
+            <ns0:gs pos="100000">
+              <ns0:schemeClr val="phClr">
+                <ns0:shade val="94000"/>
+                <ns0:satMod val="135000"/>
+              </ns0:schemeClr>
+            </ns0:gs>
+          </ns0:gsLst>
+          <ns0:lin ang="16200000" scaled="0"/>
+        </ns0:gradFill>
+      </ns0:fillStyleLst>
+      <ns0:lnStyleLst>
+        <ns0:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <ns0:solidFill>
+            <ns0:schemeClr val="phClr">
+              <ns0:shade val="95000"/>
+              <ns0:satMod val="105000"/>
+            </ns0:schemeClr>
+          </ns0:solidFill>
+          <ns0:prstDash val="solid"/>
+        </ns0:ln>
+        <ns0:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <ns0:solidFill>
+            <ns0:schemeClr val="phClr"/>
+          </ns0:solidFill>
+          <ns0:prstDash val="solid"/>
+        </ns0:ln>
+        <ns0:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <ns0:solidFill>
+            <ns0:schemeClr val="phClr"/>
+          </ns0:solidFill>
+          <ns0:prstDash val="solid"/>
+        </ns0:ln>
+      </ns0:lnStyleLst>
+      <ns0:effectStyleLst>
+        <ns0:effectStyle>
+          <ns0:effectLst>
+            <ns0:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <ns0:srgbClr val="000000">
+                <ns0:alpha val="38000"/>
+              </ns0:srgbClr>
+            </ns0:outerShdw>
+          </ns0:effectLst>
+        </ns0:effectStyle>
+        <ns0:effectStyle>
+          <ns0:effectLst>
+            <ns0:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <ns0:srgbClr val="000000">
+                <ns0:alpha val="35000"/>
+              </ns0:srgbClr>
+            </ns0:outerShdw>
+          </ns0:effectLst>
+        </ns0:effectStyle>
+        <ns0:effectStyle>
+          <ns0:effectLst>
+            <ns0:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <ns0:srgbClr val="000000">
+                <ns0:alpha val="35000"/>
+              </ns0:srgbClr>
+            </ns0:outerShdw>
+          </ns0:effectLst>
+          <ns0:scene3d>
+            <ns0:camera prst="orthographicFront">
+              <ns0:rot lat="0" lon="0" rev="0"/>
+            </ns0:camera>
+            <ns0:lightRig rig="threePt" dir="t">
+              <ns0:rot lat="0" lon="0" rev="1200000"/>
+            </ns0:lightRig>
+          </ns0:scene3d>
+          <ns0:sp3d>
+            <ns0:bevelT w="63500" h="25400"/>
+          </ns0:sp3d>
+        </ns0:effectStyle>
+      </ns0:effectStyleLst>
+      <ns0:bgFillStyleLst>
+        <ns0:solidFill>
+          <ns0:schemeClr val="phClr"/>
+        </ns0:solidFill>
+        <ns0:gradFill rotWithShape="1">
+          <ns0:gsLst>
+            <ns0:gs pos="0">
+              <ns0:schemeClr val="phClr">
+                <ns0:tint val="40000"/>
+                <ns0:satMod val="350000"/>
+              </ns0:schemeClr>
+            </ns0:gs>
+            <ns0:gs pos="40000">
+              <ns0:schemeClr val="phClr">
+                <ns0:tint val="45000"/>
+                <ns0:shade val="99000"/>
+                <ns0:satMod val="350000"/>
+              </ns0:schemeClr>
+            </ns0:gs>
+            <ns0:gs pos="100000">
+              <ns0:schemeClr val="phClr">
+                <ns0:shade val="20000"/>
+                <ns0:satMod val="255000"/>
+              </ns0:schemeClr>
+            </ns0:gs>
+          </ns0:gsLst>
+          <ns0:path path="circle">
+            <ns0:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </ns0:path>
+        </ns0:gradFill>
+        <ns0:gradFill rotWithShape="1">
+          <ns0:gsLst>
+            <ns0:gs pos="0">
+              <ns0:schemeClr val="phClr">
+                <ns0:tint val="80000"/>
+                <ns0:satMod val="300000"/>
+              </ns0:schemeClr>
+            </ns0:gs>
+            <ns0:gs pos="100000">
+              <ns0:schemeClr val="phClr">
+                <ns0:shade val="30000"/>
+                <ns0:satMod val="200000"/>
+              </ns0:schemeClr>
+            </ns0:gs>
+          </ns0:gsLst>
+          <ns0:path path="circle">
+            <ns0:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </ns0:path>
+        </ns0:gradFill>
+      </ns0:bgFillStyleLst>
+    </ns0:fmtScheme>
+  </ns0:themeElements>
+  <ns0:objectDefaults/>
+  <ns0:extraClrSchemeLst/>
+</ns0:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -570,7 +779,7 @@
     <col width="35" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="42" customHeight="1">
+    <row r="1" ht="52" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>ПРОБНЫЙ СВОДНЫЙ РЕЕСТР</t>
@@ -583,7 +792,6 @@
       <c r="F1" s="2" t="n"/>
       <c r="G1" s="2" t="n"/>
       <c r="H1" s="2" t="n"/>
-      <c r="I1" s="2" t="n"/>
     </row>
     <row r="2" ht="29" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
@@ -615,415 +823,426 @@
       <c r="H3" s="6" t="n"/>
       <c r="I3" s="6" t="n"/>
     </row>
+    <row r="4" ht="6" customHeight="1">
+      <c r="A4" s="7" t="n"/>
+      <c r="B4" s="7" t="n"/>
+      <c r="C4" s="7" t="n"/>
+      <c r="D4" s="7" t="n"/>
+      <c r="E4" s="7" t="n"/>
+      <c r="F4" s="8" t="n"/>
+      <c r="G4" s="8" t="n"/>
+      <c r="H4" s="8" t="n"/>
+      <c r="I4" s="8" t="n"/>
+    </row>
     <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>Код темы</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>Тема</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C5" s="9" t="inlineStr">
         <is>
           <t>Программа</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D5" s="9" t="inlineStr">
         <is>
           <t>ФИО лектора</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="9" t="inlineStr">
         <is>
           <t>Готовность</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="F5" s="9" t="inlineStr">
         <is>
           <t>Комментарий</t>
         </is>
       </c>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="G5" s="9" t="inlineStr">
         <is>
           <t>Требует уточнения</t>
         </is>
       </c>
-      <c r="H5" s="7" t="inlineStr">
+      <c r="H5" s="9" t="inlineStr">
         <is>
           <t>Дата анкеты</t>
         </is>
       </c>
-      <c r="I5" s="7" t="inlineStr">
+      <c r="I5" s="9" t="inlineStr">
         <is>
           <t>Файл ответа</t>
         </is>
       </c>
     </row>
     <row r="6" ht="68" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>T-2565E443</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>Введение в LDAP</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>ПТИБ (advance)</t>
         </is>
       </c>
-      <c r="D6" s="8" t="inlineStr">
+      <c r="D6" s="10" t="inlineStr">
         <is>
           <t>Демо-лектор 2 (вымышленный)</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="E6" s="10" t="inlineStr">
         <is>
           <t>Да</t>
         </is>
       </c>
-      <c r="F6" s="8" t="inlineStr"/>
-      <c r="G6" s="8" t="inlineStr"/>
-      <c r="H6" s="8" t="inlineStr">
+      <c r="F6" s="10" t="inlineStr"/>
+      <c r="G6" s="10" t="inlineStr"/>
+      <c r="H6" s="10" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="I6" s="8" t="inlineStr">
+      <c r="I6" s="10" t="inlineStr">
         <is>
           <t>02_Пример_ответа_лектора_2.xlsx</t>
         </is>
       </c>
     </row>
     <row r="7" ht="68" customHeight="1">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>T-34BD901C</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>Доменная аутентификация. Типовые атаки на протоколы аутентификации</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C7" s="11" t="inlineStr">
         <is>
           <t>ПТИБ (advance)</t>
         </is>
       </c>
-      <c r="D7" s="9" t="inlineStr">
+      <c r="D7" s="11" t="inlineStr">
         <is>
           <t>Демо-лектор 1 (вымышленный)</t>
         </is>
       </c>
-      <c r="E7" s="9" t="inlineStr">
+      <c r="E7" s="11" t="inlineStr">
         <is>
           <t>Да</t>
         </is>
       </c>
-      <c r="F7" s="9" t="inlineStr"/>
-      <c r="G7" s="9" t="inlineStr"/>
-      <c r="H7" s="9" t="inlineStr">
+      <c r="F7" s="11" t="inlineStr"/>
+      <c r="G7" s="11" t="inlineStr"/>
+      <c r="H7" s="11" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="I7" s="9" t="inlineStr">
+      <c r="I7" s="11" t="inlineStr">
         <is>
           <t>01_Пример_ответа_лектора_1.xlsx</t>
         </is>
       </c>
     </row>
     <row r="8" ht="68" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>T-C7476F67</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>Кибербезопасность, информационная безопасность, защита информации. Опыт противодействия киберпреступности (на примере Республики Беларусь и Российской Федерации)</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>ПТИБ (advance)</t>
         </is>
       </c>
-      <c r="D8" s="8" t="inlineStr">
+      <c r="D8" s="10" t="inlineStr">
         <is>
           <t>Демо-лектор 1 (вымышленный)</t>
         </is>
       </c>
-      <c r="E8" s="8" t="inlineStr">
+      <c r="E8" s="10" t="inlineStr">
         <is>
           <t>Да</t>
         </is>
       </c>
-      <c r="F8" s="8" t="inlineStr"/>
-      <c r="G8" s="8" t="inlineStr"/>
-      <c r="H8" s="8" t="inlineStr">
+      <c r="F8" s="10" t="inlineStr"/>
+      <c r="G8" s="10" t="inlineStr"/>
+      <c r="H8" s="10" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="I8" s="8" t="inlineStr">
+      <c r="I8" s="10" t="inlineStr">
         <is>
           <t>01_Пример_ответа_лектора_1.xlsx</t>
         </is>
       </c>
     </row>
     <row r="9" ht="68" customHeight="1">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>T-6F75FEB6</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>Продвинутые кибератаки. Матрица MITRE ATT&amp;CK. Модель Cyber Kill Chain. Индикаторы компрометации</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C9" s="11" t="inlineStr">
         <is>
           <t>ПТИБ (advance)</t>
         </is>
       </c>
-      <c r="D9" s="9" t="inlineStr">
+      <c r="D9" s="11" t="inlineStr">
         <is>
           <t>Демо-лектор 1 (вымышленный)</t>
         </is>
       </c>
-      <c r="E9" s="9" t="inlineStr">
+      <c r="E9" s="11" t="inlineStr">
         <is>
           <t>Частично</t>
         </is>
       </c>
-      <c r="F9" s="9" t="inlineStr">
+      <c r="F9" s="11" t="inlineStr">
         <is>
           <t>Готов читать часть про MITRE ATT&amp;CK; остальное нужно согласовать.</t>
         </is>
       </c>
-      <c r="G9" s="9" t="inlineStr">
+      <c r="G9" s="11" t="inlineStr">
         <is>
           <t>Да: уточнить объём</t>
         </is>
       </c>
-      <c r="H9" s="9" t="inlineStr">
+      <c r="H9" s="11" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="I9" s="9" t="inlineStr">
+      <c r="I9" s="11" t="inlineStr">
         <is>
           <t>01_Пример_ответа_лектора_1.xlsx</t>
         </is>
       </c>
     </row>
     <row r="10" ht="68" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>T-6F75FEB6</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>Продвинутые кибератаки. Матрица MITRE ATT&amp;CK. Модель Cyber Kill Chain. Индикаторы компрометации</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="10" t="inlineStr">
         <is>
           <t>ПТИБ (advance)</t>
         </is>
       </c>
-      <c r="D10" s="8" t="inlineStr">
+      <c r="D10" s="10" t="inlineStr">
         <is>
           <t>Демо-лектор 2 (вымышленный)</t>
         </is>
       </c>
-      <c r="E10" s="8" t="inlineStr">
+      <c r="E10" s="10" t="inlineStr">
         <is>
           <t>Да</t>
         </is>
       </c>
-      <c r="F10" s="8" t="inlineStr"/>
-      <c r="G10" s="8" t="inlineStr"/>
-      <c r="H10" s="8" t="inlineStr">
+      <c r="F10" s="10" t="inlineStr"/>
+      <c r="G10" s="10" t="inlineStr"/>
+      <c r="H10" s="10" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="I10" s="8" t="inlineStr">
+      <c r="I10" s="10" t="inlineStr">
         <is>
           <t>02_Пример_ответа_лектора_2.xlsx</t>
         </is>
       </c>
     </row>
     <row r="11" ht="68" customHeight="1">
-      <c r="A11" s="9" t="inlineStr">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>T-DF262806</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>Расследование и реагирование на атаку в инфраструктуре</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C11" s="11" t="inlineStr">
         <is>
           <t>ПТИБ (advance)</t>
         </is>
       </c>
-      <c r="D11" s="9" t="inlineStr">
+      <c r="D11" s="11" t="inlineStr">
         <is>
           <t>Демо-лектор 2 (вымышленный)</t>
         </is>
       </c>
-      <c r="E11" s="9" t="inlineStr">
+      <c r="E11" s="11" t="inlineStr">
         <is>
           <t>Частично</t>
         </is>
       </c>
-      <c r="F11" s="9" t="inlineStr">
+      <c r="F11" s="11" t="inlineStr">
         <is>
           <t>Готов вести разбор кейса совместно со вторым преподавателем.</t>
         </is>
       </c>
-      <c r="G11" s="9" t="inlineStr">
+      <c r="G11" s="11" t="inlineStr">
         <is>
           <t>Да: уточнить объём</t>
         </is>
       </c>
-      <c r="H11" s="9" t="inlineStr">
+      <c r="H11" s="11" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="I11" s="9" t="inlineStr">
+      <c r="I11" s="11" t="inlineStr">
         <is>
           <t>02_Пример_ответа_лектора_2.xlsx</t>
         </is>
       </c>
     </row>
     <row r="12" ht="68" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>T-05085C3F</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>Современный SOC</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="10" t="inlineStr">
         <is>
           <t>ПТИБ (advance)</t>
         </is>
       </c>
-      <c r="D12" s="8" t="inlineStr">
+      <c r="D12" s="10" t="inlineStr">
         <is>
           <t>Демо-лектор 1 (вымышленный)</t>
         </is>
       </c>
-      <c r="E12" s="8" t="inlineStr">
+      <c r="E12" s="10" t="inlineStr">
         <is>
           <t>Да</t>
         </is>
       </c>
-      <c r="F12" s="8" t="inlineStr"/>
-      <c r="G12" s="8" t="inlineStr"/>
-      <c r="H12" s="8" t="inlineStr">
+      <c r="F12" s="10" t="inlineStr"/>
+      <c r="G12" s="10" t="inlineStr"/>
+      <c r="H12" s="10" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="I12" s="8" t="inlineStr">
+      <c r="I12" s="10" t="inlineStr">
         <is>
           <t>01_Пример_ответа_лектора_1.xlsx</t>
         </is>
       </c>
     </row>
     <row r="13" ht="68" customHeight="1">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>T-05085C3F</t>
         </is>
       </c>
-      <c r="B13" s="9" t="inlineStr">
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>Современный SOC</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C13" s="11" t="inlineStr">
         <is>
           <t>ПТИБ (advance)</t>
         </is>
       </c>
-      <c r="D13" s="9" t="inlineStr">
+      <c r="D13" s="11" t="inlineStr">
         <is>
           <t>Демо-лектор 2 (вымышленный)</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr">
+      <c r="E13" s="11" t="inlineStr">
         <is>
           <t>Да</t>
         </is>
       </c>
-      <c r="F13" s="9" t="inlineStr"/>
-      <c r="G13" s="9" t="inlineStr"/>
-      <c r="H13" s="9" t="inlineStr">
+      <c r="F13" s="11" t="inlineStr"/>
+      <c r="G13" s="11" t="inlineStr"/>
+      <c r="H13" s="11" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="I13" s="9" t="inlineStr">
+      <c r="I13" s="11" t="inlineStr">
         <is>
           <t>02_Пример_ответа_лектора_2.xlsx</t>
         </is>
       </c>
     </row>
     <row r="14" ht="68" customHeight="1">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>T-2222062A</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="10" t="inlineStr">
         <is>
           <t>Управление пользователями</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
+      <c r="C14" s="10" t="inlineStr">
         <is>
           <t>ПТИБ (advance)</t>
         </is>
       </c>
-      <c r="D14" s="8" t="inlineStr">
+      <c r="D14" s="10" t="inlineStr">
         <is>
           <t>Демо-лектор 2 (вымышленный)</t>
         </is>
       </c>
-      <c r="E14" s="8" t="inlineStr">
+      <c r="E14" s="10" t="inlineStr">
         <is>
           <t>Да</t>
         </is>
       </c>
-      <c r="F14" s="8" t="inlineStr"/>
-      <c r="G14" s="8" t="inlineStr"/>
-      <c r="H14" s="8" t="inlineStr">
+      <c r="F14" s="10" t="inlineStr"/>
+      <c r="G14" s="10" t="inlineStr"/>
+      <c r="H14" s="10" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="I14" s="8" t="inlineStr">
+      <c r="I14" s="10" t="inlineStr">
         <is>
           <t>02_Пример_ответа_лектора_2.xlsx</t>
         </is>
@@ -1031,22 +1250,23 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A1:I1"/>
     <mergeCell ref="A3:I3"/>
     <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.35" bottom="0.35" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;CПробная версия • &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;Crozum · Пробная версия · &amp;P / &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
@@ -1069,7 +1289,7 @@
     <col width="26" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="42" customHeight="1">
+    <row r="1" ht="52" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>КАТАЛОГ ТЕМ</t>
@@ -1080,7 +1300,6 @@
       <c r="D1" s="2" t="n"/>
       <c r="E1" s="2" t="n"/>
       <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
     </row>
     <row r="2" ht="28" customHeight="1">
       <c r="A2" s="5" t="inlineStr">
@@ -1095,424 +1314,433 @@
       <c r="F2" s="6" t="n"/>
       <c r="G2" s="6" t="n"/>
     </row>
+    <row r="4" ht="6" customHeight="1">
+      <c r="A4" s="7" t="n"/>
+      <c r="B4" s="7" t="n"/>
+      <c r="C4" s="7" t="n"/>
+      <c r="D4" s="7" t="n"/>
+      <c r="E4" s="8" t="n"/>
+      <c r="F4" s="8" t="n"/>
+      <c r="G4" s="8" t="n"/>
+    </row>
     <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>Код темы</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>Тема</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C5" s="9" t="inlineStr">
         <is>
           <t>Программа</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D5" s="9" t="inlineStr">
         <is>
           <t>Содержание</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="9" t="inlineStr">
         <is>
           <t>Да</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="F5" s="9" t="inlineStr">
         <is>
           <t>Частично</t>
         </is>
       </c>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="G5" s="9" t="inlineStr">
         <is>
           <t>Покрытие темы</t>
         </is>
       </c>
     </row>
     <row r="6" ht="96" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>T-C7476F67</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>Кибербезопасность, информационная безопасность, защита информации. Опыт противодействия киберпреступности (на примере Республики Беларусь и Российской Федерации)</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>ПТИБ (advance)</t>
         </is>
       </c>
-      <c r="D6" s="8" t="inlineStr">
+      <c r="D6" s="10" t="inlineStr">
         <is>
           <t>Киберпреступность. Международный опыт противодействия киберпреступности. Построение системы обеспечения кибербезопасности в Республике Беларусь и Российской Федерации.</t>
         </is>
       </c>
-      <c r="E6" s="8" t="n">
+      <c r="E6" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="F6" s="8" t="n">
+      <c r="F6" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="G6" s="8" t="inlineStr">
+      <c r="G6" s="10" t="inlineStr">
         <is>
           <t>Есть подтверждение</t>
         </is>
       </c>
     </row>
     <row r="7" ht="96" customHeight="1">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>T-AB58E916</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>Типовая корпоративная информационная система</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C7" s="11" t="inlineStr">
         <is>
           <t>ПТИБ (advance)</t>
         </is>
       </c>
-      <c r="D7" s="9" t="inlineStr">
+      <c r="D7" s="11" t="inlineStr">
         <is>
           <t>Типовая корпоративная информационная система (далее – ИС), которая представляет собой комплекс программных и аппаратных средств, предназначенных для автоматизации бизнес-процессов в организации. Основные компоненты системы, структура, принципы построения и внедрения.</t>
         </is>
       </c>
-      <c r="E7" s="9" t="n">
+      <c r="E7" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="9" t="n">
+      <c r="F7" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="G7" s="9" t="inlineStr">
+      <c r="G7" s="11" t="inlineStr">
         <is>
           <t>Нет отметок</t>
         </is>
       </c>
     </row>
     <row r="8" ht="96" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>T-6F75FEB6</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>Продвинутые кибератаки. Матрица MITRE ATT&amp;CK. Модель Cyber Kill Chain. Индикаторы компрометации</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>ПТИБ (advance)</t>
         </is>
       </c>
-      <c r="D8" s="8" t="inlineStr">
+      <c r="D8" s="10" t="inlineStr">
         <is>
           <t>Матрица MITRE ATT&amp;CK. Модель Cyber Kill Chain. Детектирование инцидентов. Работа с индикаторами компрометации.</t>
         </is>
       </c>
-      <c r="E8" s="8" t="n">
+      <c r="E8" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="F8" s="8" t="n">
+      <c r="F8" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="G8" s="8" t="inlineStr">
+      <c r="G8" s="10" t="inlineStr">
         <is>
           <t>Есть подтверждение</t>
         </is>
       </c>
     </row>
     <row r="9" ht="96" customHeight="1">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>T-05085C3F</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>Современный SOC</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C9" s="11" t="inlineStr">
         <is>
           <t>ПТИБ (advance)</t>
         </is>
       </c>
-      <c r="D9" s="9" t="inlineStr">
+      <c r="D9" s="11" t="inlineStr">
         <is>
           <t>Эволюция SOC, триада (люди, процессы, технологии), уровни процессов, метрики, роли сотрудников (L1–L3, инженеры, архитектор, руководитель), RACI-матрица, технологии (SIEM, EDR/XDR, SOAR, TI), AI и Agentic SOC.</t>
         </is>
       </c>
-      <c r="E9" s="9" t="n">
+      <c r="E9" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="F9" s="9" t="n">
+      <c r="F9" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="G9" s="9" t="inlineStr">
+      <c r="G9" s="11" t="inlineStr">
         <is>
           <t>Есть подтверждение</t>
         </is>
       </c>
     </row>
     <row r="10" ht="96" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>T-8A73AE5B</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>Жизненный цикл информационной безопасности</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="10" t="inlineStr">
         <is>
           <t>ПТИБ (advance)</t>
         </is>
       </c>
-      <c r="D10" s="8" t="inlineStr">
+      <c r="D10" s="10" t="inlineStr">
         <is>
           <t>Определения, связанные с информационной безопасностью (ИБ). Этапы жизненного цикла.</t>
         </is>
       </c>
-      <c r="E10" s="8" t="n">
+      <c r="E10" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="F10" s="8" t="n">
+      <c r="F10" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="G10" s="8" t="inlineStr">
+      <c r="G10" s="10" t="inlineStr">
         <is>
           <t>Нет отметок</t>
         </is>
       </c>
     </row>
     <row r="11" ht="96" customHeight="1">
-      <c r="A11" s="9" t="inlineStr">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>T-815E59FB</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>Анализ журналов и популярных событий Windows</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C11" s="11" t="inlineStr">
         <is>
           <t>ПТИБ (advance)</t>
         </is>
       </c>
-      <c r="D11" s="9" t="inlineStr">
+      <c r="D11" s="11" t="inlineStr">
         <is>
           <t>Инструменты анализа журналов Windows: Event Viewer (фильтры, XML), EvtxECmd (парсинг), Timeline Explorer (просмотр CSV), Get-WinEvent и Wevtutil (консоль), Hayabusa (поиск угроз по Sigma-правилам).</t>
         </is>
       </c>
-      <c r="E11" s="9" t="n">
+      <c r="E11" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="F11" s="9" t="n">
+      <c r="F11" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="G11" s="9" t="inlineStr">
+      <c r="G11" s="11" t="inlineStr">
         <is>
           <t>Нет отметок</t>
         </is>
       </c>
     </row>
     <row r="12" ht="96" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>T-E7421B02</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>Домены Active Directory. Доменная групповая политика</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="10" t="inlineStr">
         <is>
           <t>ПТИБ (advance)</t>
         </is>
       </c>
-      <c r="D12" s="8" t="inlineStr">
+      <c r="D12" s="10" t="inlineStr">
         <is>
           <t>Типовая корпоративная ИС. Основные компоненты ИС, структура, принципы построения и внедрения.
 Концепция доменов в Active Directory (далее – AD). Основные принципы работы доменов, структура, роли контроллера домена.</t>
         </is>
       </c>
-      <c r="E12" s="8" t="n">
+      <c r="E12" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="F12" s="8" t="n">
+      <c r="F12" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="G12" s="8" t="inlineStr">
+      <c r="G12" s="10" t="inlineStr">
         <is>
           <t>Нет отметок</t>
         </is>
       </c>
     </row>
     <row r="13" ht="96" customHeight="1">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>T-34BD901C</t>
         </is>
       </c>
-      <c r="B13" s="9" t="inlineStr">
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>Доменная аутентификация. Типовые атаки на протоколы аутентификации</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C13" s="11" t="inlineStr">
         <is>
           <t>ПТИБ (advance)</t>
         </is>
       </c>
-      <c r="D13" s="9" t="inlineStr">
+      <c r="D13" s="11" t="inlineStr">
         <is>
           <t>Процесс аутентификации пользователей и компьютеров в домене Active Directory. Методы аутентификации, протоколы, используемые для передачи учетных данных, механизмы защиты от несанкционированного доступа.</t>
         </is>
       </c>
-      <c r="E13" s="9" t="n">
+      <c r="E13" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="F13" s="9" t="n">
+      <c r="F13" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="G13" s="9" t="inlineStr">
+      <c r="G13" s="11" t="inlineStr">
         <is>
           <t>Есть подтверждение</t>
         </is>
       </c>
     </row>
     <row r="14" ht="96" customHeight="1">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>T-2565E443</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="10" t="inlineStr">
         <is>
           <t>Введение в LDAP</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
+      <c r="C14" s="10" t="inlineStr">
         <is>
           <t>ПТИБ (advance)</t>
         </is>
       </c>
-      <c r="D14" s="8" t="inlineStr">
+      <c r="D14" s="10" t="inlineStr">
         <is>
           <t>LDAP (Lightweight Directory Access Protocol): основные понятия и принципы работы LDAP.</t>
         </is>
       </c>
-      <c r="E14" s="8" t="n">
+      <c r="E14" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="F14" s="8" t="n">
+      <c r="F14" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="G14" s="8" t="inlineStr">
+      <c r="G14" s="10" t="inlineStr">
         <is>
           <t>Есть подтверждение</t>
         </is>
       </c>
     </row>
     <row r="15" ht="96" customHeight="1">
-      <c r="A15" s="9" t="inlineStr">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t>T-2222062A</t>
         </is>
       </c>
-      <c r="B15" s="9" t="inlineStr">
+      <c r="B15" s="11" t="inlineStr">
         <is>
           <t>Управление пользователями</t>
         </is>
       </c>
-      <c r="C15" s="9" t="inlineStr">
+      <c r="C15" s="11" t="inlineStr">
         <is>
           <t>ПТИБ (advance)</t>
         </is>
       </c>
-      <c r="D15" s="9" t="inlineStr">
+      <c r="D15" s="11" t="inlineStr">
         <is>
           <t>Создание, изменение, удаление пользователей. Ключевые объектные классы пользователей. Настройка атрибутов пользователей и групп. Использование LDIF для управления. Особенности кодирования в LDIF. Безопасность пользователей.</t>
         </is>
       </c>
-      <c r="E15" s="9" t="n">
+      <c r="E15" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="F15" s="9" t="n">
+      <c r="F15" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="G15" s="9" t="inlineStr">
+      <c r="G15" s="11" t="inlineStr">
         <is>
           <t>Есть подтверждение</t>
         </is>
       </c>
     </row>
     <row r="16" ht="96" customHeight="1">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>T-DF262806</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>Расследование и реагирование на атаку в инфраструктуре</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
+      <c r="C16" s="10" t="inlineStr">
         <is>
           <t>ПТИБ (advance)</t>
         </is>
       </c>
-      <c r="D16" s="8" t="inlineStr">
+      <c r="D16" s="10" t="inlineStr">
         <is>
           <t>Сбор и анализ артефактов инцидента на узлах и в сетевой инфраструктуре. Выявление вектора компрометации и определение последовательности действий нарушителя. Локализация инцидента, сдерживание распространения атаки и восстановление работоспособности сервисов. Отработка типового сценария расследования и реагирования на атаку.</t>
         </is>
       </c>
-      <c r="E16" s="8" t="n">
+      <c r="E16" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="F16" s="8" t="n">
+      <c r="F16" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="G16" s="8" t="inlineStr">
+      <c r="G16" s="10" t="inlineStr">
         <is>
           <t>Только частично</t>
         </is>
       </c>
     </row>
     <row r="17" ht="96" customHeight="1">
-      <c r="A17" s="9" t="inlineStr">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t>T-1EBBC04E</t>
         </is>
       </c>
-      <c r="B17" s="9" t="inlineStr">
+      <c r="B17" s="11" t="inlineStr">
         <is>
           <t>Отработка сценария «атака вируса-шифровальщика» на киберполигоне. Анализ результатов, обсуждение и разбор сценария</t>
         </is>
       </c>
-      <c r="C17" s="9" t="inlineStr">
+      <c r="C17" s="11" t="inlineStr">
         <is>
           <t>ПТИБ (advance)</t>
         </is>
       </c>
-      <c r="D17" s="9" t="inlineStr">
+      <c r="D17" s="11" t="inlineStr">
         <is>
           <t>Расследования инцидента «атака вируса-шифровальщика» в инфраструктуре. Идентификация всех этапов атаки, определение всех индикаторов компрометации.
 Сценарий самостоятельной работы:
@@ -1520,13 +1748,13 @@
 закрепление навыков оформления отчетных материалов по результатам расследования инцидента.</t>
         </is>
       </c>
-      <c r="E17" s="9" t="n">
+      <c r="E17" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="F17" s="9" t="n">
+      <c r="F17" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="G17" s="9" t="inlineStr">
+      <c r="G17" s="11" t="inlineStr">
         <is>
           <t>Нет отметок</t>
         </is>
@@ -1535,20 +1763,21 @@
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.35" bottom="0.35" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;CПробная версия • &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;Crozum · Пробная версия · &amp;P / &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
@@ -1570,7 +1799,7 @@
     <col width="46" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="42" customHeight="1">
+    <row r="1" ht="52" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>ПОЛУЧЕННЫЕ АНКЕТЫ</t>
@@ -1580,7 +1809,6 @@
       <c r="C1" s="2" t="n"/>
       <c r="D1" s="2" t="n"/>
       <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
     </row>
     <row r="2" ht="28" customHeight="1">
       <c r="A2" s="5" t="inlineStr">
@@ -1594,89 +1822,97 @@
       <c r="E2" s="6" t="n"/>
       <c r="F2" s="6" t="n"/>
     </row>
+    <row r="4" ht="6" customHeight="1">
+      <c r="A4" s="7" t="n"/>
+      <c r="B4" s="7" t="n"/>
+      <c r="C4" s="7" t="n"/>
+      <c r="D4" s="8" t="n"/>
+      <c r="E4" s="8" t="n"/>
+      <c r="F4" s="8" t="n"/>
+    </row>
     <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>ФИО лектора</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>Дата анкеты</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C5" s="9" t="inlineStr">
         <is>
           <t>Заполнение</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D5" s="9" t="inlineStr">
         <is>
           <t>Тем полностью</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="9" t="inlineStr">
         <is>
           <t>Тем частично</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="F5" s="9" t="inlineStr">
         <is>
           <t>Файл ответа</t>
         </is>
       </c>
     </row>
     <row r="6" ht="45" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Демо-лектор 1 (вымышленный)</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>Выбор завершён</t>
         </is>
       </c>
-      <c r="D6" s="8" t="n">
+      <c r="D6" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="E6" s="8" t="n">
+      <c r="E6" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="F6" s="8" t="inlineStr">
+      <c r="F6" s="10" t="inlineStr">
         <is>
           <t>01_Пример_ответа_лектора_1.xlsx</t>
         </is>
       </c>
     </row>
     <row r="7" ht="45" customHeight="1">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>Демо-лектор 2 (вымышленный)</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C7" s="11" t="inlineStr">
         <is>
           <t>Выбор завершён</t>
         </is>
       </c>
-      <c r="D7" s="9" t="n">
+      <c r="D7" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="E7" s="9" t="n">
+      <c r="E7" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="F7" s="9" t="inlineStr">
+      <c r="F7" s="11" t="inlineStr">
         <is>
           <t>02_Пример_ответа_лектора_2.xlsx</t>
         </is>
@@ -1685,20 +1921,21 @@
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.35" bottom="0.35" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;CПробная версия • &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;Crozum · Пробная версия · &amp;P / &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
@@ -1718,7 +1955,7 @@
     <col width="46" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="42" customHeight="1">
+    <row r="1" ht="52" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>ПРОГРАММЫ</t>
@@ -1726,7 +1963,6 @@
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
     </row>
     <row r="2" ht="29" customHeight="1">
       <c r="A2" s="5" t="inlineStr">
@@ -1738,45 +1974,51 @@
       <c r="C2" s="6" t="n"/>
       <c r="D2" s="6" t="n"/>
     </row>
+    <row r="4" ht="6" customHeight="1">
+      <c r="A4" s="7" t="n"/>
+      <c r="B4" s="7" t="n"/>
+      <c r="C4" s="8" t="n"/>
+      <c r="D4" s="8" t="n"/>
+    </row>
     <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>Код программы</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>Сокращение</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C5" s="9" t="inlineStr">
         <is>
           <t>Полное название программы</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D5" s="9" t="inlineStr">
         <is>
           <t>Файл-источник</t>
         </is>
       </c>
     </row>
     <row r="6" ht="72" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>P-PTIB-ADV</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>ПТИБ (advance)</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>ПРАКТИЧЕСКОЕ ПРИМЕНЕНИЕ ТЕХНОЛОГИЙ ИНФОРМАЦИОННОЙ БЕЗОПАСНОСТИ (+КИБЕРУЧЕНИЯ) (ADVANCE)</t>
         </is>
       </c>
-      <c r="D6" s="8" t="inlineStr">
+      <c r="D6" s="10" t="inlineStr">
         <is>
           <t>sample-program-template.docx</t>
         </is>
@@ -1784,21 +2026,22 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:C1"/>
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.35" bottom="0.35" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;CПробная версия • &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;Crozum · Пробная версия · &amp;P / &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
@@ -1820,7 +2063,7 @@
     <col width="28" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="42" customHeight="1">
+    <row r="1" ht="52" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>ПОЯСНЕНИЯ</t>
@@ -1830,19 +2073,18 @@
       <c r="C1" s="2" t="n"/>
       <c r="D1" s="2" t="n"/>
       <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
     </row>
     <row r="3" ht="47" customHeight="1">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Это демонстрация объединения специально заполненных копий. ФИО вымышлены. Прежние назначения из «Тема-Лектор_1» не использованы.</t>
         </is>
       </c>
-      <c r="B3" s="11" t="n"/>
-      <c r="C3" s="11" t="n"/>
-      <c r="D3" s="11" t="n"/>
-      <c r="E3" s="11" t="n"/>
-      <c r="F3" s="11" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
     </row>
     <row r="4" ht="47" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
@@ -1857,16 +2099,16 @@
       <c r="F4" s="6" t="n"/>
     </row>
     <row r="5" ht="47" customHeight="1">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>Полная готовность «Да» и частичная готовность различаются. При частичной готовности организатор уточняет объём, даже если есть комментарий.</t>
         </is>
       </c>
-      <c r="B5" s="11" t="n"/>
-      <c r="C5" s="11" t="n"/>
-      <c r="D5" s="11" t="n"/>
-      <c r="E5" s="11" t="n"/>
-      <c r="F5" s="11" t="n"/>
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
     </row>
     <row r="6" ht="47" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
@@ -1881,16 +2123,16 @@
       <c r="F6" s="6" t="n"/>
     </row>
     <row r="7" ht="47" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>Одинаковые копии одного ФИО учитываются один раз. Если два файла одного ФИО отличаются, объединение останавливается: актуальный ответ нужно выбрать явно.</t>
         </is>
       </c>
-      <c r="B7" s="11" t="n"/>
-      <c r="C7" s="11" t="n"/>
-      <c r="D7" s="11" t="n"/>
-      <c r="E7" s="11" t="n"/>
-      <c r="F7" s="11" t="n"/>
+      <c r="B7" s="2" t="n"/>
+      <c r="C7" s="2" t="n"/>
+      <c r="D7" s="2" t="n"/>
+      <c r="E7" s="2" t="n"/>
+      <c r="F7" s="2" t="n"/>
     </row>
     <row r="8" ht="47" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
@@ -1905,16 +2147,16 @@
       <c r="F8" s="6" t="n"/>
     </row>
     <row r="9" ht="47" customHeight="1">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>Для нового свода загрузите полученные анкеты в чат. Для самостоятельного объединения есть служебный скрипт и инструкция рядом с файлами.</t>
         </is>
       </c>
-      <c r="B9" s="11" t="n"/>
-      <c r="C9" s="11" t="n"/>
-      <c r="D9" s="11" t="n"/>
-      <c r="E9" s="11" t="n"/>
-      <c r="F9" s="11" t="n"/>
+      <c r="B9" s="2" t="n"/>
+      <c r="C9" s="2" t="n"/>
+      <c r="D9" s="2" t="n"/>
+      <c r="E9" s="2" t="n"/>
+      <c r="F9" s="2" t="n"/>
     </row>
     <row r="10" ht="47" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
@@ -1929,26 +2171,26 @@
       <c r="F10" s="6" t="n"/>
     </row>
     <row r="11" ht="47" customHeight="1">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>Содержание взято из локального образца, не из Google Drive. Пробный каталог содержит одну программу; проверка межпрограммных совпадений ещё не выполнена.</t>
         </is>
       </c>
-      <c r="B11" s="11" t="n"/>
-      <c r="C11" s="11" t="n"/>
-      <c r="D11" s="11" t="n"/>
-      <c r="E11" s="11" t="n"/>
-      <c r="F11" s="11" t="n"/>
+      <c r="B11" s="2" t="n"/>
+      <c r="C11" s="2" t="n"/>
+      <c r="D11" s="2" t="n"/>
+      <c r="E11" s="2" t="n"/>
+      <c r="F11" s="2" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="10">
     <mergeCell ref="A11:F11"/>
     <mergeCell ref="A10:F10"/>
-    <mergeCell ref="A1:F1"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="A9:F9"/>
     <mergeCell ref="A8:F8"/>
     <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A1:E1"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A7:F7"/>
@@ -1957,11 +2199,12 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;CПробная версия • &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;Crozum · Пробная версия · &amp;P / &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>